--- a/stad_MyPractice/src/test/resources/excel_File/MyPracticeExcel.xlsx
+++ b/stad_MyPractice/src/test/resources/excel_File/MyPracticeExcel.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>SrNo</t>
   </si>
@@ -180,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -191,6 +191,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="1">
@@ -506,7 +507,7 @@
       <c r="C2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>22</v>
       </c>
     </row>

--- a/stad_MyPractice/src/test/resources/excel_File/MyPracticeExcel.xlsx
+++ b/stad_MyPractice/src/test/resources/excel_File/MyPracticeExcel.xlsx
@@ -3,7 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{F8701D78-BF26-4F7A-9E47-7F09C80D211A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34b2ea137c607895/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="28" documentId="11_F25DC773A252ABDACC1048B7711956AA5ADE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E94FEEB5-FB24-42AB-854D-4F427ED34E02}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,9 +16,8 @@
     <sheet name="NaveenSite" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <oleSize ref="A1"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -30,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>SrNo</t>
   </si>
@@ -96,16 +100,12 @@
   </si>
   <si>
     <t>TestCaseId</t>
-  </si>
-  <si>
-    <t>TC001 :Passed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -129,7 +129,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -140,16 +140,6 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="17"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="17"/>
       </patternFill>
     </fill>
   </fills>
@@ -180,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -191,8 +181,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -476,11 +464,11 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="2" width="8.88671875"/>
-    <col min="2" max="2" customWidth="true" style="2" width="12.0"/>
-    <col min="3" max="3" customWidth="true" style="2" width="101.88671875"/>
-    <col min="4" max="4" customWidth="true" style="2" width="10.0"/>
-    <col min="5" max="16384" style="2" width="8.88671875"/>
+    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="12" style="2" customWidth="1"/>
+    <col min="3" max="3" width="101.88671875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -507,9 +495,7 @@
       <c r="C2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
